--- a/xslx/empresas_con_descripcion_corto.xlsx
+++ b/xslx/empresas_con_descripcion_corto.xlsx
@@ -649,7 +649,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="2" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="2" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="s">
         <v>13</v>
       </c>
@@ -691,7 +691,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="3" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="3" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A3" s="1" t="s">
         <v>25</v>
       </c>
@@ -737,7 +737,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="4" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="4" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="s">
         <v>37</v>
       </c>
@@ -825,7 +825,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="6" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="6" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="s">
         <v>55</v>
       </c>
@@ -870,7 +870,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="7" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="7" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="s">
         <v>67</v>
       </c>
@@ -910,7 +910,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="8" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="8" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="s">
         <v>75</v>
       </c>
@@ -956,7 +956,7 @@
         <v>83</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="46.25" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="47.45" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="s">
         <v>84</v>
       </c>
